--- a/tame_output/ON/bt/strategyON_20241011.xlsx
+++ b/tame_output/ON/bt/strategyON_20241011.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2109</v>
+        <v>2110</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>50.8%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>101.0%</t>
+          <t>101.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2109</v>
+        <v>2110</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-9.1%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>84.2%</t>
+          <t>84.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>145.2%</t>
+          <t>146.6%</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2109</v>
+        <v>2110</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.7%</t>
+          <t>-74.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.5%</t>
+          <t>88.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-675.1%</t>
+          <t>-675.8%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2109</v>
+        <v>2110</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-10.0%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-124.8%</t>
+          <t>-123.8%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2109</v>
+        <v>2110</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.1%</t>
+          <t>-24.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-113.0%</t>
+          <t>-113.8%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>108.7%</t>
+          <t>108.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2109</v>
+        <v>2110</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-19.1%</t>
+          <t>-19.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>98.2%</t>
+          <t>98.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>78.3%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2112"/>
+  <dimension ref="A1:G2113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50121,7 +50121,7 @@
         <v>45574</v>
       </c>
       <c r="B2112" t="n">
-        <v>3.793046482686237</v>
+        <v>3.791976669481232</v>
       </c>
       <c r="C2112" t="n">
         <v>4.568546364114659</v>
@@ -50137,6 +50137,29 @@
       </c>
       <c r="G2112" t="n">
         <v>5.234585228751375</v>
+      </c>
+    </row>
+    <row r="2113">
+      <c r="A2113" s="2" t="n">
+        <v>45575</v>
+      </c>
+      <c r="B2113" t="n">
+        <v>3.78896214346813</v>
+      </c>
+      <c r="C2113" t="n">
+        <v>4.582101927173098</v>
+      </c>
+      <c r="D2113" t="n">
+        <v>-5.1427568733708</v>
+      </c>
+      <c r="E2113" t="n">
+        <v>2.524642753511031</v>
+      </c>
+      <c r="F2113" t="n">
+        <v>1.102166608744787</v>
+      </c>
+      <c r="G2113" t="n">
+        <v>5.243401892419971</v>
       </c>
     </row>
   </sheetData>
